--- a/tensile_samples_data.xlsx
+++ b/tensile_samples_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,17 +501,17 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Axial_strain</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Lateral_strain</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Modulus_of_Elasticity</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Lateral_strain</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Axial_strain</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
@@ -567,43 +567,43 @@
         <v>0.474</v>
       </c>
       <c r="G2" t="n">
-        <v>3877.3536532</v>
+        <v>3877.354</v>
       </c>
       <c r="H2" t="n">
         <v>49436.258</v>
       </c>
       <c r="I2" t="n">
-        <v>2.634</v>
+        <v>2.814</v>
       </c>
       <c r="J2" t="n">
-        <v>1.004</v>
+        <v>1.188</v>
       </c>
       <c r="K2" t="n">
-        <v>2.66</v>
+        <v>2.848</v>
       </c>
       <c r="L2" t="n">
-        <v>20.295062</v>
+        <v>20.296</v>
       </c>
       <c r="M2" t="n">
         <v>10.47</v>
       </c>
       <c r="N2" t="n">
-        <v>130.226</v>
+        <v>139.02</v>
       </c>
       <c r="O2" t="n">
+        <v>0.0014982</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.00038918</v>
+      </c>
+      <c r="Q2" t="n">
         <v>36.87</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.0003912</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.001502</v>
       </c>
       <c r="R2" t="n">
         <v>0.26</v>
       </c>
       <c r="S2" t="n">
-        <v>14.63</v>
+        <v>15.69</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
         <v>55.472</v>
       </c>
       <c r="V2" t="n">
-        <v>9.220000000000001</v>
+        <v>15.22</v>
       </c>
       <c r="W2" t="n">
         <v>37.89</v>
@@ -640,43 +640,43 @@
         <v>0.454</v>
       </c>
       <c r="G3" t="n">
-        <v>3717.1324278</v>
+        <v>3717.132</v>
       </c>
       <c r="H3" t="n">
         <v>47393.438</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>2.824</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9620000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="K3" t="n">
-        <v>2.686</v>
+        <v>2.856</v>
       </c>
       <c r="L3" t="n">
-        <v>18.61995</v>
+        <v>18.62</v>
       </c>
       <c r="M3" t="n">
         <v>10.026</v>
       </c>
       <c r="N3" t="n">
-        <v>126.01</v>
+        <v>133.95</v>
       </c>
       <c r="O3" t="n">
-        <v>45.826</v>
+        <v>0.001364</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002754</v>
+        <v>0.00034902</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001122</v>
+        <v>37.318</v>
       </c>
       <c r="R3" t="n">
-        <v>0.242</v>
+        <v>0.254</v>
       </c>
       <c r="S3" t="n">
-        <v>18.494</v>
+        <v>15.974</v>
       </c>
       <c r="T3" t="n">
         <v>0.26</v>
@@ -685,10 +685,10 @@
         <v>50.884</v>
       </c>
       <c r="V3" t="n">
-        <v>9.102</v>
+        <v>14.1</v>
       </c>
       <c r="W3" t="n">
-        <v>37.114</v>
+        <v>36.73</v>
       </c>
     </row>
     <row r="4">
@@ -713,43 +713,43 @@
         <v>0.454</v>
       </c>
       <c r="G4" t="n">
-        <v>3717.1324276</v>
+        <v>3717.132</v>
       </c>
       <c r="H4" t="n">
         <v>47393.438</v>
       </c>
       <c r="I4" t="n">
-        <v>2.542</v>
+        <v>2.802</v>
       </c>
       <c r="J4" t="n">
-        <v>1.376</v>
+        <v>1.224</v>
       </c>
       <c r="K4" t="n">
-        <v>2.576</v>
+        <v>2.834</v>
       </c>
       <c r="L4" t="n">
-        <v>18.180144</v>
+        <v>18.182</v>
       </c>
       <c r="M4" t="n">
         <v>9.794</v>
       </c>
       <c r="N4" t="n">
-        <v>120.166</v>
+        <v>132.862</v>
       </c>
       <c r="O4" t="n">
-        <v>37.75</v>
+        <v>0.0009921999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.000255</v>
+        <v>0.00024278</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.00102</v>
+        <v>38.81</v>
       </c>
       <c r="R4" t="n">
-        <v>0.25</v>
+        <v>0.244</v>
       </c>
       <c r="S4" t="n">
-        <v>15.1</v>
+        <v>16.814</v>
       </c>
       <c r="T4" t="n">
         <v>0.52</v>
@@ -758,10 +758,10 @@
         <v>38.514</v>
       </c>
       <c r="V4" t="n">
-        <v>5.31</v>
+        <v>11.31</v>
       </c>
       <c r="W4" t="n">
-        <v>33.97</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="5">
@@ -786,43 +786,43 @@
         <v>0.43</v>
       </c>
       <c r="G5" t="n">
-        <v>3524.8669575</v>
+        <v>3524.8675</v>
       </c>
       <c r="H5" t="n">
         <v>44942.05</v>
       </c>
       <c r="I5" t="n">
-        <v>2.57</v>
+        <v>2.8575</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2325</v>
+        <v>0.985</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6025</v>
+        <v>2.8875</v>
       </c>
       <c r="L5" t="n">
-        <v>16.0940225</v>
+        <v>16.0975</v>
       </c>
       <c r="M5" t="n">
         <v>9.147500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>115.265</v>
+        <v>128.285</v>
       </c>
       <c r="O5" t="n">
-        <v>41.65</v>
+        <v>0.001064</v>
       </c>
       <c r="P5" t="n">
-        <v>0.000276</v>
+        <v>0.00024545</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.00112</v>
+        <v>41.6475</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2425</v>
+        <v>0.2325</v>
       </c>
       <c r="S5" t="n">
-        <v>16.7825</v>
+        <v>18.115</v>
       </c>
       <c r="T5" t="n">
         <v>0.79</v>
@@ -831,7 +831,7 @@
         <v>45.0675</v>
       </c>
       <c r="V5" t="n">
-        <v>5.6775</v>
+        <v>11.68</v>
       </c>
       <c r="W5" t="n">
         <v>34.95</v>
@@ -859,43 +859,43 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>3418.052807</v>
+        <v>3418.056666666667</v>
       </c>
       <c r="H6" t="n">
         <v>43580.17000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7399999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="K6" t="n">
-        <v>2.813333333333334</v>
+        <v>2.82</v>
       </c>
       <c r="L6" t="n">
-        <v>13.52160333333333</v>
+        <v>13.52</v>
       </c>
       <c r="M6" t="n">
         <v>7.909999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>121.56</v>
+        <v>121.1966666666667</v>
       </c>
       <c r="O6" t="n">
-        <v>44.03</v>
+        <v>0.001069666666666667</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002333333333333333</v>
+        <v>0.0002349333333333333</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.00111</v>
+        <v>45.76666666666667</v>
       </c>
       <c r="R6" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="S6" t="n">
-        <v>18.19</v>
+        <v>19.63333333333333</v>
       </c>
       <c r="T6" t="n">
         <v>1.05</v>
@@ -904,10 +904,10 @@
         <v>48.95</v>
       </c>
       <c r="V6" t="n">
-        <v>3.27</v>
+        <v>10.27</v>
       </c>
       <c r="W6" t="n">
-        <v>33.97</v>
+        <v>35.49</v>
       </c>
     </row>
     <row r="7">
@@ -932,43 +932,43 @@
         <v>0.4675</v>
       </c>
       <c r="G7" t="n">
-        <v>3825.2817545</v>
+        <v>3825.2825</v>
       </c>
       <c r="H7" t="n">
         <v>48772.3425</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6825</v>
+        <v>2.845</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8825000000000001</v>
+        <v>1.055</v>
       </c>
       <c r="K7" t="n">
-        <v>2.705</v>
+        <v>2.875</v>
       </c>
       <c r="L7" t="n">
-        <v>14.5655125</v>
+        <v>14.565</v>
       </c>
       <c r="M7" t="n">
         <v>7.63</v>
       </c>
       <c r="N7" t="n">
-        <v>130.995</v>
+        <v>138.915</v>
       </c>
       <c r="O7" t="n">
-        <v>43.25</v>
+        <v>0.0012285</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00041125</v>
+        <v>0.00026115</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00142</v>
+        <v>49.9675</v>
       </c>
       <c r="R7" t="n">
-        <v>0.29</v>
+        <v>0.215</v>
       </c>
       <c r="S7" t="n">
-        <v>16.76</v>
+        <v>20.9125</v>
       </c>
       <c r="T7" t="n">
         <v>1.31</v>
@@ -977,10 +977,10 @@
         <v>61.3425</v>
       </c>
       <c r="V7" t="n">
-        <v>10.76</v>
+        <v>15.66</v>
       </c>
       <c r="W7" t="n">
-        <v>36.65</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="8">
@@ -1005,43 +1005,43 @@
         <v>0.395</v>
       </c>
       <c r="G8" t="n">
-        <v>3244.47981325</v>
+        <v>3244.4775</v>
       </c>
       <c r="H8" t="n">
         <v>41367.11500000001</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6225</v>
+        <v>2.8025</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0875</v>
+        <v>1.255</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6525</v>
+        <v>2.84</v>
       </c>
       <c r="L8" t="n">
-        <v>12.97652</v>
+        <v>12.975</v>
       </c>
       <c r="M8" t="n">
         <v>8</v>
       </c>
       <c r="N8" t="n">
-        <v>108.3525</v>
+        <v>115.9625</v>
       </c>
       <c r="O8" t="n">
-        <v>51.85</v>
+        <v>0.00130325</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00027325</v>
+        <v>0.0002744</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0013025</v>
+        <v>51.8525</v>
       </c>
       <c r="R8" t="n">
         <v>0.21</v>
       </c>
       <c r="S8" t="n">
-        <v>21.43</v>
+        <v>21.425</v>
       </c>
       <c r="T8" t="n">
         <v>1.57</v>
@@ -1050,10 +1050,10 @@
         <v>67.46250000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>10.76</v>
+        <v>16.86</v>
       </c>
       <c r="W8" t="n">
-        <v>36.65</v>
+        <v>36.76</v>
       </c>
     </row>
     <row r="9">
@@ -1078,43 +1078,43 @@
         <v>0.4366666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>3578.274032333333</v>
+        <v>3578.276666666667</v>
       </c>
       <c r="H9" t="n">
         <v>45622.99</v>
       </c>
       <c r="I9" t="n">
-        <v>2.953333333333333</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="J9" t="n">
-        <v>0.75</v>
+        <v>1.893333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>2.97</v>
+        <v>2.77</v>
       </c>
       <c r="L9" t="n">
-        <v>17.10815333333333</v>
+        <v>17.11</v>
       </c>
       <c r="M9" t="n">
         <v>9.57</v>
       </c>
       <c r="N9" t="n">
-        <v>134.52</v>
+        <v>123.9366666666667</v>
       </c>
       <c r="O9" t="n">
-        <v>32.71</v>
+        <v>0.00124</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002476666666666667</v>
+        <v>0.0002482</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001236666666666667</v>
+        <v>32.71333333333333</v>
       </c>
       <c r="R9" t="n">
         <v>0.2</v>
       </c>
       <c r="S9" t="n">
-        <v>13.63</v>
+        <v>6.760000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1123,10 +1123,10 @@
         <v>40.50666666666667</v>
       </c>
       <c r="V9" t="n">
-        <v>5.94</v>
+        <v>11.94</v>
       </c>
       <c r="W9" t="n">
-        <v>28.03</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="10">
@@ -1151,43 +1151,43 @@
         <v>0.4433333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>3631.681107666667</v>
+        <v>3631.683333333333</v>
       </c>
       <c r="H10" t="n">
         <v>46303.93</v>
       </c>
       <c r="I10" t="n">
-        <v>2.613333333333333</v>
+        <v>2.74</v>
       </c>
       <c r="J10" t="n">
-        <v>1.276666666666667</v>
+        <v>1.696666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.65</v>
+        <v>2.783333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>15.26320666666667</v>
+        <v>15.26333333333333</v>
       </c>
       <c r="M10" t="n">
         <v>8.436666666666666</v>
       </c>
       <c r="N10" t="n">
-        <v>120.94</v>
+        <v>126.92</v>
       </c>
       <c r="O10" t="n">
-        <v>25.24</v>
+        <v>0.001420333333333333</v>
       </c>
       <c r="P10" t="n">
-        <v>0.000303</v>
+        <v>0.0002458666666666667</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001596666666666667</v>
+        <v>28.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0.19</v>
+        <v>0.1733333333333333</v>
       </c>
       <c r="S10" t="n">
-        <v>10.61</v>
+        <v>6.953333333333333</v>
       </c>
       <c r="T10" t="n">
         <v>0.26</v>
@@ -1196,10 +1196,10 @@
         <v>40.29333333333333</v>
       </c>
       <c r="V10" t="n">
-        <v>5.94</v>
+        <v>11.61</v>
       </c>
       <c r="W10" t="n">
-        <v>28.03</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="11">
@@ -1224,43 +1224,43 @@
         <v>0.4433333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>3631.681107666667</v>
+        <v>3631.683333333333</v>
       </c>
       <c r="H11" t="n">
         <v>46303.93</v>
       </c>
       <c r="I11" t="n">
-        <v>2.653333333333333</v>
+        <v>2.75</v>
       </c>
       <c r="J11" t="n">
-        <v>1.223333333333333</v>
+        <v>1.673333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>2.686666666666666</v>
+        <v>2.796666666666667</v>
       </c>
       <c r="L11" t="n">
-        <v>14.72486333333333</v>
+        <v>14.72333333333333</v>
       </c>
       <c r="M11" t="n">
         <v>8.106666666666667</v>
       </c>
       <c r="N11" t="n">
-        <v>122.8533333333333</v>
+        <v>127.3766666666667</v>
       </c>
       <c r="O11" t="n">
-        <v>25.28</v>
+        <v>0.001252333333333333</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0001993333333333333</v>
+        <v>0.0001693</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.00111</v>
+        <v>22.24333333333333</v>
       </c>
       <c r="R11" t="n">
-        <v>0.18</v>
+        <v>0.1366666666666667</v>
       </c>
       <c r="S11" t="n">
-        <v>10.71</v>
+        <v>7.55</v>
       </c>
       <c r="T11" t="n">
         <v>0.52</v>
@@ -1269,10 +1269,10 @@
         <v>28.02666666666667</v>
       </c>
       <c r="V11" t="n">
-        <v>3.08</v>
+        <v>9.08</v>
       </c>
       <c r="W11" t="n">
-        <v>24.01</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="12">
@@ -1297,43 +1297,43 @@
         <v>0.4233333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>3471.459882333333</v>
+        <v>3471.463333333333</v>
       </c>
       <c r="H12" t="n">
         <v>44261.11000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>2.786666666666667</v>
+        <v>2.716666666666667</v>
       </c>
       <c r="J12" t="n">
-        <v>1.013333333333333</v>
+        <v>1.876666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>2.816666666666666</v>
+        <v>2.766666666666667</v>
       </c>
       <c r="L12" t="n">
-        <v>11.92847</v>
+        <v>11.93</v>
       </c>
       <c r="M12" t="n">
         <v>6.859999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>123.3266666666667</v>
+        <v>120.3166666666667</v>
       </c>
       <c r="O12" t="n">
+        <v>0.001305</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0001546</v>
+      </c>
+      <c r="Q12" t="n">
         <v>19.67</v>
       </c>
-      <c r="P12" t="n">
-        <v>0.000222</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.001303333333333333</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="S12" t="n">
-        <v>8.41</v>
+        <v>8.549999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>0.79</v>
@@ -1342,10 +1342,10 @@
         <v>25.66666666666667</v>
       </c>
       <c r="V12" t="n">
-        <v>2.29</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>24.01</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="13">
@@ -1370,43 +1370,43 @@
         <v>0.45</v>
       </c>
       <c r="G13" t="n">
-        <v>3685.088182666666</v>
+        <v>3685.09</v>
       </c>
       <c r="H13" t="n">
         <v>46984.87</v>
       </c>
       <c r="I13" t="n">
-        <v>2.663333333333334</v>
+        <v>2.753333333333333</v>
       </c>
       <c r="J13" t="n">
-        <v>1.21</v>
+        <v>1.416666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>2.693333333333333</v>
+        <v>2.793333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>10.85338666666667</v>
+        <v>10.85333333333333</v>
       </c>
       <c r="M13" t="n">
         <v>5.899999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>124.92</v>
+        <v>129.34</v>
       </c>
       <c r="O13" t="n">
-        <v>27.17</v>
+        <v>0.001777333333333333</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000244</v>
+        <v>0.0002206333333333333</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.001353333333333333</v>
+        <v>20.74</v>
       </c>
       <c r="R13" t="n">
-        <v>0.18</v>
+        <v>0.1233333333333333</v>
       </c>
       <c r="S13" t="n">
-        <v>11.51</v>
+        <v>9.853333333333333</v>
       </c>
       <c r="T13" t="n">
         <v>1.05</v>
@@ -1415,7 +1415,7 @@
         <v>36.83000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>3.24</v>
+        <v>9.24</v>
       </c>
       <c r="W13" t="n">
         <v>27.81</v>
@@ -1443,43 +1443,43 @@
         <v>0.43</v>
       </c>
       <c r="G14" t="n">
-        <v>3524.86695725</v>
+        <v>3524.87</v>
       </c>
       <c r="H14" t="n">
         <v>44942.05</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9675</v>
+        <v>2.7575</v>
       </c>
       <c r="J14" t="n">
-        <v>0.74</v>
+        <v>1.43</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9875</v>
+        <v>2.8</v>
       </c>
       <c r="L14" t="n">
-        <v>6.14188</v>
+        <v>6.1425</v>
       </c>
       <c r="M14" t="n">
         <v>3.4675</v>
       </c>
       <c r="N14" t="n">
-        <v>132.8225</v>
+        <v>123.9475</v>
       </c>
       <c r="O14" t="n">
-        <v>20.19</v>
+        <v>0.00162175</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000314</v>
+        <v>0.000236125</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.00196</v>
+        <v>24.4575</v>
       </c>
       <c r="R14" t="n">
-        <v>0.16</v>
+        <v>0.1425</v>
       </c>
       <c r="S14" t="n">
-        <v>8.699999999999999</v>
+        <v>11.1025</v>
       </c>
       <c r="T14" t="n">
         <v>1.31</v>
@@ -1488,10 +1488,10 @@
         <v>39.6025</v>
       </c>
       <c r="V14" t="n">
-        <v>6.31</v>
+        <v>12.15</v>
       </c>
       <c r="W14" t="n">
-        <v>30.97</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="15">
@@ -1516,37 +1516,37 @@
         <v>0.4433333333333334</v>
       </c>
       <c r="G15" t="n">
-        <v>3631.681107333334</v>
+        <v>3631.683333333333</v>
       </c>
       <c r="H15" t="n">
         <v>46303.93</v>
       </c>
       <c r="I15" t="n">
-        <v>2.646666666666667</v>
+        <v>2.73</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="K15" t="n">
-        <v>2.683333333333334</v>
+        <v>2.773333333333333</v>
       </c>
       <c r="L15" t="n">
-        <v>9.086679999999999</v>
+        <v>9.083333333333334</v>
       </c>
       <c r="M15" t="n">
         <v>5.003333333333334</v>
       </c>
       <c r="N15" t="n">
-        <v>122.8333333333333</v>
+        <v>126.45</v>
       </c>
       <c r="O15" t="n">
+        <v>0.001606333333333334</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.0002572</v>
+      </c>
+      <c r="Q15" t="n">
         <v>26.98</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.0002566666666666667</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.001606666666666667</v>
       </c>
       <c r="R15" t="n">
         <v>0.16</v>
@@ -1561,10 +1561,10 @@
         <v>43.33000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>6.31</v>
+        <v>12.52</v>
       </c>
       <c r="W15" t="n">
-        <v>30.97</v>
+        <v>30.32</v>
       </c>
     </row>
   </sheetData>

--- a/tensile_samples_data.xlsx
+++ b/tensile_samples_data.xlsx
@@ -591,25 +591,25 @@
         <v>139.02</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0014982</v>
+        <v>0.00149636</v>
       </c>
       <c r="P2" t="n">
-        <v>0.00038918</v>
+        <v>0.00038906</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.87</v>
+        <v>38.4</v>
       </c>
       <c r="R2" t="n">
         <v>0.26</v>
       </c>
       <c r="S2" t="n">
-        <v>15.69</v>
+        <v>15.2381</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>55.472</v>
+        <v>57.472</v>
       </c>
       <c r="V2" t="n">
         <v>15.22</v>
@@ -664,10 +664,10 @@
         <v>133.95</v>
       </c>
       <c r="O3" t="n">
-        <v>0.001364</v>
+        <v>0.00136398</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00034902</v>
+        <v>0.0003467</v>
       </c>
       <c r="Q3" t="n">
         <v>37.318</v>
@@ -676,7 +676,7 @@
         <v>0.254</v>
       </c>
       <c r="S3" t="n">
-        <v>15.974</v>
+        <v>14.88068</v>
       </c>
       <c r="T3" t="n">
         <v>0.26</v>
@@ -737,10 +737,10 @@
         <v>132.862</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0009921999999999999</v>
+        <v>0.00108514</v>
       </c>
       <c r="P4" t="n">
-        <v>0.00024278</v>
+        <v>0.00026476</v>
       </c>
       <c r="Q4" t="n">
         <v>38.81</v>
@@ -749,13 +749,13 @@
         <v>0.244</v>
       </c>
       <c r="S4" t="n">
-        <v>16.814</v>
+        <v>15.59916</v>
       </c>
       <c r="T4" t="n">
         <v>0.52</v>
       </c>
       <c r="U4" t="n">
-        <v>38.514</v>
+        <v>42.114</v>
       </c>
       <c r="V4" t="n">
         <v>11.31</v>
@@ -810,10 +810,10 @@
         <v>128.285</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001064</v>
+        <v>0.00116185</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00024545</v>
+        <v>0.00027035</v>
       </c>
       <c r="Q5" t="n">
         <v>41.6475</v>
@@ -822,13 +822,13 @@
         <v>0.2325</v>
       </c>
       <c r="S5" t="n">
-        <v>18.115</v>
+        <v>16.904075</v>
       </c>
       <c r="T5" t="n">
         <v>0.79</v>
       </c>
       <c r="U5" t="n">
-        <v>45.0675</v>
+        <v>48.5675</v>
       </c>
       <c r="V5" t="n">
         <v>11.68</v>
@@ -883,10 +883,10 @@
         <v>121.1966666666667</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001069666666666667</v>
+        <v>0.001069366666666667</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0002349333333333333</v>
+        <v>0.0002352333333333333</v>
       </c>
       <c r="Q6" t="n">
         <v>45.76666666666667</v>
@@ -895,7 +895,7 @@
         <v>0.22</v>
       </c>
       <c r="S6" t="n">
-        <v>19.63333333333333</v>
+        <v>18.75683333333333</v>
       </c>
       <c r="T6" t="n">
         <v>1.05</v>
@@ -956,10 +956,10 @@
         <v>138.915</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0012285</v>
+        <v>0.0012283</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00026115</v>
+        <v>0.0002643</v>
       </c>
       <c r="Q7" t="n">
         <v>49.9675</v>
@@ -968,7 +968,7 @@
         <v>0.215</v>
       </c>
       <c r="S7" t="n">
-        <v>20.9125</v>
+        <v>20.56955</v>
       </c>
       <c r="T7" t="n">
         <v>1.31</v>
@@ -1029,19 +1029,19 @@
         <v>115.9625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00130325</v>
+        <v>0.001265725</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002744</v>
+        <v>0.000266675</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.8525</v>
+        <v>53.375</v>
       </c>
       <c r="R8" t="n">
         <v>0.21</v>
       </c>
       <c r="S8" t="n">
-        <v>21.425</v>
+        <v>22.066475</v>
       </c>
       <c r="T8" t="n">
         <v>1.57</v>
@@ -1102,25 +1102,25 @@
         <v>123.9366666666667</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00124</v>
+        <v>0.001288066666666667</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0002482</v>
+        <v>0.0002964666666666667</v>
       </c>
       <c r="Q9" t="n">
-        <v>32.71333333333333</v>
+        <v>33</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="S9" t="n">
-        <v>6.760000000000001</v>
+        <v>13.41523333333333</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>40.50666666666667</v>
+        <v>42.50666666666667</v>
       </c>
       <c r="V9" t="n">
         <v>11.94</v>
@@ -1175,19 +1175,19 @@
         <v>126.92</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001420333333333333</v>
+        <v>0.001420433333333333</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0002458666666666667</v>
+        <v>0.0002695</v>
       </c>
       <c r="Q10" t="n">
         <v>28.36</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1733333333333333</v>
+        <v>0.19</v>
       </c>
       <c r="S10" t="n">
-        <v>6.953333333333333</v>
+        <v>11.9185</v>
       </c>
       <c r="T10" t="n">
         <v>0.26</v>
@@ -1248,19 +1248,19 @@
         <v>127.3766666666667</v>
       </c>
       <c r="O11" t="n">
-        <v>0.001252333333333333</v>
+        <v>0.001252366666666667</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0001693</v>
+        <v>0.0002014666666666666</v>
       </c>
       <c r="Q11" t="n">
         <v>22.24333333333333</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1366666666666667</v>
+        <v>0.16</v>
       </c>
       <c r="S11" t="n">
-        <v>7.55</v>
+        <v>9.585366666666667</v>
       </c>
       <c r="T11" t="n">
         <v>0.52</v>
@@ -1321,25 +1321,25 @@
         <v>120.3166666666667</v>
       </c>
       <c r="O12" t="n">
-        <v>0.001305</v>
+        <v>0.0009651333333333334</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001546</v>
+        <v>0.0001447</v>
       </c>
       <c r="Q12" t="n">
         <v>19.67</v>
       </c>
       <c r="R12" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="S12" t="n">
-        <v>8.549999999999999</v>
+        <v>8.552566666666666</v>
       </c>
       <c r="T12" t="n">
         <v>0.79</v>
       </c>
       <c r="U12" t="n">
-        <v>25.66666666666667</v>
+        <v>18.98333333333333</v>
       </c>
       <c r="V12" t="n">
         <v>8.289999999999999</v>
@@ -1394,19 +1394,19 @@
         <v>129.34</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001777333333333333</v>
+        <v>0.001777466666666667</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0002206333333333333</v>
+        <v>0.0002669333333333333</v>
       </c>
       <c r="Q13" t="n">
         <v>20.74</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1233333333333333</v>
+        <v>0.15</v>
       </c>
       <c r="S13" t="n">
-        <v>9.853333333333333</v>
+        <v>9.019733333333333</v>
       </c>
       <c r="T13" t="n">
         <v>1.05</v>
@@ -1458,10 +1458,10 @@
         <v>2.8</v>
       </c>
       <c r="L14" t="n">
-        <v>6.1425</v>
+        <v>6.5825</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4675</v>
+        <v>3.7175</v>
       </c>
       <c r="N14" t="n">
         <v>123.9475</v>
@@ -1470,16 +1470,16 @@
         <v>0.00162175</v>
       </c>
       <c r="P14" t="n">
-        <v>0.000236125</v>
+        <v>0.000264</v>
       </c>
       <c r="Q14" t="n">
         <v>24.4575</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1425</v>
+        <v>0.1625</v>
       </c>
       <c r="S14" t="n">
-        <v>11.1025</v>
+        <v>10.52345</v>
       </c>
       <c r="T14" t="n">
         <v>1.31</v>
@@ -1540,25 +1540,25 @@
         <v>126.45</v>
       </c>
       <c r="O15" t="n">
-        <v>0.001606333333333334</v>
+        <v>0.001723966666666667</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0002572</v>
+        <v>0.0003272666666666667</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.98</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="S15" t="n">
-        <v>11.63</v>
+        <v>11.97536666666667</v>
       </c>
       <c r="T15" t="n">
         <v>1.57</v>
       </c>
       <c r="U15" t="n">
-        <v>43.33000000000001</v>
+        <v>49.13333333333333</v>
       </c>
       <c r="V15" t="n">
         <v>12.52</v>
